--- a/GameDesign/Excel/Artifact.xlsx
+++ b/GameDesign/Excel/Artifact.xlsx
@@ -599,7 +599,7 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>lstring</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
